--- a/Versão5/ELET/Ontologia_Elétrica.xlsx
+++ b/Versão5/ELET/Ontologia_Elétrica.xlsx
@@ -4282,7 +4282,7 @@
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46213.785332523148</v>
+        <v>46214.369187037039</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>93</v>

--- a/Versão5/ELET/Ontologia_Elétrica.xlsx
+++ b/Versão5/ELET/Ontologia_Elétrica.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ELET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD35BEB6-F925-439D-A4AE-A2699B343090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2290E83A-A830-4B64-8B94-304F0F99DD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -2256,9 +2256,6 @@
     <t>Segmento.de.Bandeja.de.Cabos</t>
   </si>
   <si>
-    <t>EletroTécnico</t>
-  </si>
-  <si>
     <t>00Super
 Class
 5</t>
@@ -2303,13 +2300,16 @@
     <t>quem.fabricou</t>
   </si>
   <si>
-    <t>Conceito</t>
-  </si>
-  <si>
     <t>Contêineres</t>
   </si>
   <si>
     <t>[ 5I ]</t>
+  </si>
+  <si>
+    <t>Conceitos</t>
+  </si>
+  <si>
+    <t>EletroTécnicos</t>
   </si>
 </sst>
 </file>
@@ -2864,71 +2864,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="86">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="79">
     <dxf>
       <font>
         <b val="0"/>
@@ -4134,14 +4070,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="33.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="43" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.69140625" customWidth="1"/>
+    <col min="2" max="2" width="33.69140625" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>43</v>
       </c>
@@ -4152,7 +4088,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>45</v>
       </c>
@@ -4163,7 +4099,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>47</v>
       </c>
@@ -4174,7 +4110,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>48</v>
       </c>
@@ -4185,7 +4121,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>49</v>
       </c>
@@ -4197,7 +4133,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>50</v>
       </c>
@@ -4209,7 +4145,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>51</v>
       </c>
@@ -4220,7 +4156,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="39" t="s">
         <v>53</v>
       </c>
@@ -4231,7 +4167,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>54</v>
       </c>
@@ -4242,7 +4178,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>56</v>
       </c>
@@ -4253,7 +4189,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>58</v>
       </c>
@@ -4264,7 +4200,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>59</v>
       </c>
@@ -4275,7 +4211,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>60</v>
       </c>
@@ -4286,7 +4222,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>61</v>
       </c>
@@ -4297,7 +4233,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>62</v>
       </c>
@@ -4308,7 +4244,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>63</v>
       </c>
@@ -4319,7 +4255,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>64</v>
       </c>
@@ -4330,19 +4266,19 @@
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>65</v>
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46216.376882060184</v>
+        <v>46243.519222106479</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>66</v>
       </c>
@@ -4353,7 +4289,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>68</v>
       </c>
@@ -4364,7 +4300,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>69</v>
       </c>
@@ -4375,7 +4311,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>70</v>
       </c>
@@ -4386,7 +4322,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>71</v>
       </c>
@@ -4397,7 +4333,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
         <v>90</v>
       </c>
@@ -4418,36 +4354,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA142"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="63" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" style="63" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" style="63" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="63" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.85546875" style="69" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" customWidth="1"/>
+    <col min="2" max="2" width="5.69140625" style="63" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.15234375" style="63" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.15234375" style="63" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.53515625" style="63" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.84375" style="69" bestFit="1" customWidth="1"/>
     <col min="7" max="11" width="8" style="63" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" style="63" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.140625" style="63" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="63" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.85546875" style="63" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="72.140625" style="63" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="73.5703125" style="63" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" style="63" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="63" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.140625" style="63" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="63" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" style="63" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.7109375" style="63" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="43.7109375" style="63" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="23.85546875" style="70" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" style="63" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="67.7109375" style="63" bestFit="1" customWidth="1"/>
-    <col min="28" max="96" width="2.5703125" style="63" customWidth="1"/>
-    <col min="97" max="16384" width="9.140625" style="63"/>
+    <col min="12" max="12" width="8.15234375" style="63" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.15234375" style="63" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.53515625" style="63" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.84375" style="63" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="72.15234375" style="63" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="73.53515625" style="63" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.69140625" style="63" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.15234375" style="63" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.15234375" style="63" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.53515625" style="63" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.53515625" style="63" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.69140625" style="63" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="43.69140625" style="63" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="23.84375" style="70" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.69140625" style="63" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="67.69140625" style="63" bestFit="1" customWidth="1"/>
+    <col min="28" max="96" width="2.53515625" style="63" customWidth="1"/>
+    <col min="97" max="16384" width="9.15234375" style="63"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="45" t="s">
         <v>95</v>
       </c>
@@ -4464,7 +4400,7 @@
         <v>38</v>
       </c>
       <c r="F1" s="58" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="G1" s="47" t="s">
         <v>0</v>
@@ -4530,21 +4466,21 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="61">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>83</v>
       </c>
       <c r="E2" s="57" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="F2" s="57" t="s">
         <v>82</v>
@@ -4581,7 +4517,7 @@
         <v>Contêiner</v>
       </c>
       <c r="P2" s="31" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="Q2" s="31" t="s">
         <v>84</v>
@@ -4615,31 +4551,31 @@
         <v>9</v>
       </c>
       <c r="Z2" s="31" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="AA2" s="31" t="str">
         <f t="shared" ref="AA2:AA6" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="61">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>83</v>
       </c>
       <c r="E3" s="57" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="F3" s="57" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="G3" s="65" t="s">
         <v>9</v>
@@ -4673,7 +4609,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="31" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="Q3" s="31" t="s">
         <v>84</v>
@@ -4714,24 +4650,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="61">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>83</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="G4" s="65" t="s">
         <v>9</v>
@@ -4765,7 +4701,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="31" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="Q4" s="31" t="s">
         <v>84</v>
@@ -4806,24 +4742,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="61">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>83</v>
       </c>
       <c r="E5" s="57" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="F5" s="57" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G5" s="65" t="s">
         <v>9</v>
@@ -4857,7 +4793,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="31" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="Q5" s="31" t="s">
         <v>84</v>
@@ -4898,24 +4834,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="61">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>83</v>
       </c>
       <c r="E6" s="57" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="F6" s="57" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="G6" s="65" t="s">
         <v>9</v>
@@ -4949,7 +4885,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="31" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="Q6" s="31" t="s">
         <v>84</v>
@@ -4990,15 +4926,15 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="61">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D7" s="44" t="s">
         <v>512</v>
@@ -5026,7 +4962,7 @@
       </c>
       <c r="L7" s="35" t="str">
         <f t="shared" ref="L7:L69" si="5">CONCATENATE("", C7)</f>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M7" s="35" t="str">
         <f t="shared" ref="M7:M69" si="6">CONCATENATE("", D7)</f>
@@ -5081,15 +5017,15 @@
         <v>Electrical Lighting System</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="61">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D8" s="44" t="s">
         <v>512</v>
@@ -5117,7 +5053,7 @@
       </c>
       <c r="L8" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M8" s="35" t="str">
         <f t="shared" si="6"/>
@@ -5172,15 +5108,15 @@
         <v>Electrical Lighting System</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="61">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D9" s="44" t="s">
         <v>512</v>
@@ -5208,7 +5144,7 @@
       </c>
       <c r="L9" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M9" s="35" t="str">
         <f t="shared" si="6"/>
@@ -5263,15 +5199,15 @@
         <v>Electrical System</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="61">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D10" s="44" t="s">
         <v>512</v>
@@ -5299,7 +5235,7 @@
       </c>
       <c r="L10" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M10" s="35" t="str">
         <f t="shared" si="6"/>
@@ -5354,15 +5290,15 @@
         <v>Electric Power System</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="61">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D11" s="44" t="s">
         <v>512</v>
@@ -5390,7 +5326,7 @@
       </c>
       <c r="L11" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M11" s="35" t="str">
         <f t="shared" si="6"/>
@@ -5445,15 +5381,15 @@
         <v>Solar Generation Electric System</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="61">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>511</v>
@@ -5481,7 +5417,7 @@
       </c>
       <c r="L12" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M12" s="35" t="str">
         <f t="shared" si="6"/>
@@ -5536,15 +5472,15 @@
         <v>Location of electricity meters</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="61">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>511</v>
@@ -5572,7 +5508,7 @@
       </c>
       <c r="L13" s="35" t="str">
         <f t="shared" ref="L13" si="12">CONCATENATE("", C13)</f>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M13" s="35" t="str">
         <f t="shared" ref="M13" si="13">CONCATENATE("", D13)</f>
@@ -5627,15 +5563,15 @@
         <v>QGBT - Receives power from the grid and distributes it to smaller boards.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="61">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>511</v>
@@ -5663,7 +5599,7 @@
       </c>
       <c r="L14" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M14" s="35" t="str">
         <f t="shared" si="6"/>
@@ -5718,15 +5654,15 @@
         <v>QDC - Distributes power to final lighting circuits, outlets, air conditioning</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="61">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>511</v>
@@ -5754,7 +5690,7 @@
       </c>
       <c r="L15" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M15" s="35" t="str">
         <f t="shared" si="6"/>
@@ -5809,15 +5745,15 @@
         <v>QTA - Automatically switches between the urban grid and the building generator to ensure critical services</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="61">
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>511</v>
@@ -5845,7 +5781,7 @@
       </c>
       <c r="L16" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M16" s="35" t="str">
         <f t="shared" si="6"/>
@@ -5900,15 +5836,15 @@
         <v>QDCC - Command and Control Panel with automation devices, relays, PLCs, contactors and timers</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="61">
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>511</v>
@@ -5936,7 +5872,7 @@
       </c>
       <c r="L17" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M17" s="35" t="str">
         <f t="shared" si="6"/>
@@ -5991,15 +5927,15 @@
         <v>QDF - Powers power loads of motors, compressors, pumps</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="61">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>511</v>
@@ -6027,7 +5963,7 @@
       </c>
       <c r="L18" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M18" s="35" t="str">
         <f t="shared" si="6"/>
@@ -6082,15 +6018,15 @@
         <v>QSP - Building services such as pump controls, lighting of common areas, gates, etc.</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="61">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>511</v>
@@ -6118,7 +6054,7 @@
       </c>
       <c r="L19" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M19" s="35" t="str">
         <f t="shared" si="6"/>
@@ -6173,15 +6109,15 @@
         <v>QSOL - Photovoltaic system panel</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="61">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>511</v>
@@ -6209,7 +6145,7 @@
       </c>
       <c r="L20" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M20" s="35" t="str">
         <f t="shared" si="6"/>
@@ -6264,15 +6200,15 @@
         <v>QL - General or Emergency Lighting Panel</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="61">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>511</v>
@@ -6300,7 +6236,7 @@
       </c>
       <c r="L21" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M21" s="35" t="str">
         <f t="shared" si="6"/>
@@ -6355,15 +6291,15 @@
         <v>Junction Box</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="61">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>511</v>
@@ -6391,7 +6327,7 @@
       </c>
       <c r="L22" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M22" s="35" t="str">
         <f t="shared" si="6"/>
@@ -6446,15 +6382,15 @@
         <v>Junction Box</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="61">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>511</v>
@@ -6482,7 +6418,7 @@
       </c>
       <c r="L23" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M23" s="35" t="str">
         <f t="shared" si="6"/>
@@ -6537,15 +6473,15 @@
         <v>Switch Box</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="61">
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>511</v>
@@ -6573,7 +6509,7 @@
       </c>
       <c r="L24" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M24" s="35" t="str">
         <f t="shared" si="6"/>
@@ -6628,15 +6564,15 @@
         <v>Socket Box</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="61">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>511</v>
@@ -6664,7 +6600,7 @@
       </c>
       <c r="L25" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M25" s="35" t="str">
         <f t="shared" si="6"/>
@@ -6689,7 +6625,7 @@
       </c>
       <c r="S25" s="31" t="str">
         <f t="shared" ref="S25:S66" si="19">SUBSTITUTE(C25, "_", " ")</f>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T25" s="31" t="str">
         <f t="shared" si="9"/>
@@ -6719,15 +6655,15 @@
         <v>419</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="61">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>511</v>
@@ -6755,7 +6691,7 @@
       </c>
       <c r="L26" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M26" s="35" t="str">
         <f t="shared" si="6"/>
@@ -6780,7 +6716,7 @@
       </c>
       <c r="S26" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T26" s="31" t="str">
         <f t="shared" si="9"/>
@@ -6810,15 +6746,15 @@
         <v>420</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="61">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>511</v>
@@ -6846,7 +6782,7 @@
       </c>
       <c r="L27" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M27" s="35" t="str">
         <f t="shared" si="6"/>
@@ -6871,7 +6807,7 @@
       </c>
       <c r="S27" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T27" s="31" t="str">
         <f t="shared" si="9"/>
@@ -6901,15 +6837,15 @@
         <v>421</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="61">
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>511</v>
@@ -6937,7 +6873,7 @@
       </c>
       <c r="L28" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M28" s="35" t="str">
         <f t="shared" si="6"/>
@@ -6962,7 +6898,7 @@
       </c>
       <c r="S28" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T28" s="31" t="str">
         <f t="shared" si="9"/>
@@ -6992,15 +6928,15 @@
         <v>422</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="61">
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>511</v>
@@ -7028,7 +6964,7 @@
       </c>
       <c r="L29" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M29" s="35" t="str">
         <f t="shared" si="6"/>
@@ -7053,7 +6989,7 @@
       </c>
       <c r="S29" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T29" s="31" t="str">
         <f t="shared" si="9"/>
@@ -7083,15 +7019,15 @@
         <v>423</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="61">
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>511</v>
@@ -7119,7 +7055,7 @@
       </c>
       <c r="L30" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M30" s="35" t="str">
         <f t="shared" si="6"/>
@@ -7144,7 +7080,7 @@
       </c>
       <c r="S30" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T30" s="31" t="str">
         <f t="shared" si="9"/>
@@ -7174,15 +7110,15 @@
         <v>424</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="61">
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>511</v>
@@ -7210,7 +7146,7 @@
       </c>
       <c r="L31" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M31" s="35" t="str">
         <f t="shared" si="6"/>
@@ -7235,7 +7171,7 @@
       </c>
       <c r="S31" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T31" s="31" t="str">
         <f t="shared" si="9"/>
@@ -7265,15 +7201,15 @@
         <v>425</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="61">
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>511</v>
@@ -7301,7 +7237,7 @@
       </c>
       <c r="L32" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M32" s="35" t="str">
         <f t="shared" si="6"/>
@@ -7326,7 +7262,7 @@
       </c>
       <c r="S32" s="31" t="str">
         <f t="shared" ref="S32:S35" si="21">SUBSTITUTE(C32, "_", " ")</f>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T32" s="31" t="str">
         <f t="shared" si="9"/>
@@ -7356,15 +7292,15 @@
         <v>419</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="61">
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>511</v>
@@ -7392,7 +7328,7 @@
       </c>
       <c r="L33" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M33" s="35" t="str">
         <f t="shared" si="6"/>
@@ -7417,7 +7353,7 @@
       </c>
       <c r="S33" s="31" t="str">
         <f t="shared" ref="S33" si="23">SUBSTITUTE(C33, "_", " ")</f>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T33" s="31" t="str">
         <f t="shared" si="9"/>
@@ -7447,15 +7383,15 @@
         <v>420</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="61">
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>511</v>
@@ -7483,7 +7419,7 @@
       </c>
       <c r="L34" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M34" s="35" t="str">
         <f t="shared" si="6"/>
@@ -7508,7 +7444,7 @@
       </c>
       <c r="S34" s="31" t="str">
         <f t="shared" si="21"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T34" s="31" t="str">
         <f t="shared" si="9"/>
@@ -7538,15 +7474,15 @@
         <v>420</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="61">
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C35" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>511</v>
@@ -7574,7 +7510,7 @@
       </c>
       <c r="L35" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M35" s="35" t="str">
         <f t="shared" si="6"/>
@@ -7599,7 +7535,7 @@
       </c>
       <c r="S35" s="31" t="str">
         <f t="shared" si="21"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T35" s="31" t="str">
         <f t="shared" si="9"/>
@@ -7629,15 +7565,15 @@
         <v>419</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="61">
         <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C36" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>511</v>
@@ -7665,7 +7601,7 @@
       </c>
       <c r="L36" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M36" s="35" t="str">
         <f t="shared" si="6"/>
@@ -7690,7 +7626,7 @@
       </c>
       <c r="S36" s="31" t="str">
         <f t="shared" ref="S36:S38" si="25">SUBSTITUTE(C36, "_", " ")</f>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T36" s="31" t="str">
         <f t="shared" si="9"/>
@@ -7720,15 +7656,15 @@
         <v>419</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="61">
         <v>37</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C37" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>511</v>
@@ -7756,7 +7692,7 @@
       </c>
       <c r="L37" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M37" s="35" t="str">
         <f t="shared" si="6"/>
@@ -7781,7 +7717,7 @@
       </c>
       <c r="S37" s="31" t="str">
         <f t="shared" si="25"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T37" s="31" t="str">
         <f t="shared" si="9"/>
@@ -7811,15 +7747,15 @@
         <v>420</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="61">
         <v>38</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C38" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>511</v>
@@ -7847,7 +7783,7 @@
       </c>
       <c r="L38" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M38" s="35" t="str">
         <f t="shared" si="6"/>
@@ -7872,7 +7808,7 @@
       </c>
       <c r="S38" s="31" t="str">
         <f t="shared" si="25"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T38" s="31" t="str">
         <f t="shared" si="9"/>
@@ -7902,15 +7838,15 @@
         <v>420</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="61">
         <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C39" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>511</v>
@@ -7938,7 +7874,7 @@
       </c>
       <c r="L39" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M39" s="35" t="str">
         <f t="shared" si="6"/>
@@ -7963,7 +7899,7 @@
       </c>
       <c r="S39" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T39" s="31" t="str">
         <f t="shared" si="9"/>
@@ -7994,15 +7930,15 @@
         <v>Cable carrier segments is a flow segment used specifically to carry and support cabling.</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="61">
         <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C40" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>511</v>
@@ -8030,7 +7966,7 @@
       </c>
       <c r="L40" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M40" s="35" t="str">
         <f t="shared" si="6"/>
@@ -8055,7 +7991,7 @@
       </c>
       <c r="S40" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T40" s="31" t="str">
         <f t="shared" si="9"/>
@@ -8086,15 +8022,15 @@
         <v>Cable holder is a horizontal cable holder fixed at only one end, spaced at intervals.</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="61">
         <v>41</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C41" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>511</v>
@@ -8122,7 +8058,7 @@
       </c>
       <c r="L41" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M41" s="35" t="str">
         <f t="shared" si="6"/>
@@ -8147,7 +8083,7 @@
       </c>
       <c r="S41" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T41" s="31" t="str">
         <f t="shared" si="9"/>
@@ -8178,15 +8114,15 @@
         <v>Open carrier segments in which cables are transported on a ladder structure.</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="61">
         <v>42</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C42" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>511</v>
@@ -8214,7 +8150,7 @@
       </c>
       <c r="L42" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M42" s="35" t="str">
         <f t="shared" si="6"/>
@@ -8239,7 +8175,7 @@
       </c>
       <c r="S42" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T42" s="31" t="str">
         <f t="shared" si="9"/>
@@ -8270,15 +8206,15 @@
         <v>Carrier segments (usually) open in which cables are placed.</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="61">
         <v>43</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C43" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>511</v>
@@ -8306,7 +8242,7 @@
       </c>
       <c r="L43" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M43" s="35" t="str">
         <f t="shared" si="6"/>
@@ -8331,7 +8267,7 @@
       </c>
       <c r="S43" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T43" s="31" t="str">
         <f t="shared" si="9"/>
@@ -8362,15 +8298,15 @@
         <v>Closed carrier segments with one or more compartments in which the cables are placed.</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="61">
         <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>511</v>
@@ -8398,7 +8334,7 @@
       </c>
       <c r="L44" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M44" s="35" t="str">
         <f t="shared" si="6"/>
@@ -8423,7 +8359,7 @@
       </c>
       <c r="S44" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T44" s="31" t="str">
         <f t="shared" si="9"/>
@@ -8454,15 +8390,15 @@
         <v>Catenary wire is a longitudinal wire that supports the grooved contact wires directly or individually.</v>
       </c>
     </row>
-    <row r="45" spans="1:27" s="68" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:27" s="68" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="61">
         <v>45</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>511</v>
@@ -8490,7 +8426,7 @@
       </c>
       <c r="L45" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M45" s="35" t="str">
         <f t="shared" si="6"/>
@@ -8515,7 +8451,7 @@
       </c>
       <c r="S45" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T45" s="31" t="str">
         <f t="shared" si="9"/>
@@ -8546,15 +8482,15 @@
         <v>Enclosed tubular segments through which the cables are pulled.</v>
       </c>
     </row>
-    <row r="46" spans="1:27" s="68" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:27" s="68" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="61">
         <v>46</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C46" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>511</v>
@@ -8582,7 +8518,7 @@
       </c>
       <c r="L46" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M46" s="35" t="str">
         <f t="shared" si="6"/>
@@ -8607,7 +8543,7 @@
       </c>
       <c r="S46" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T46" s="31" t="str">
         <f t="shared" si="9"/>
@@ -8638,15 +8574,15 @@
         <v>Dropper is a cable carrier used to suspend the cable from another cable.</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="61">
         <v>47</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>511</v>
@@ -8674,7 +8610,7 @@
       </c>
       <c r="L47" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M47" s="35" t="str">
         <f t="shared" si="6"/>
@@ -8699,7 +8635,7 @@
       </c>
       <c r="S47" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T47" s="31" t="str">
         <f t="shared" si="9"/>
@@ -8730,15 +8666,15 @@
         <v>Cable holder connection is connection that is placed at the junction or transition in the cable support system.</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="61">
         <v>48</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C48" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>511</v>
@@ -8766,7 +8702,7 @@
       </c>
       <c r="L48" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M48" s="35" t="str">
         <f t="shared" si="6"/>
@@ -8791,7 +8727,7 @@
       </c>
       <c r="S48" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T48" s="31" t="str">
         <f t="shared" si="9"/>
@@ -8822,15 +8758,15 @@
         <v>Accessory that changes the route of the cable carrier.</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="61">
         <v>49</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C49" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>511</v>
@@ -8858,7 +8794,7 @@
       </c>
       <c r="L49" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M49" s="35" t="str">
         <f t="shared" si="6"/>
@@ -8883,7 +8819,7 @@
       </c>
       <c r="S49" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T49" s="31" t="str">
         <f t="shared" si="9"/>
@@ -8914,15 +8850,15 @@
         <v>Connector, usually used to join two ports within flow distribution system.</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="61">
         <v>50</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C50" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>511</v>
@@ -8950,7 +8886,7 @@
       </c>
       <c r="L50" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M50" s="35" t="str">
         <f t="shared" si="6"/>
@@ -8975,7 +8911,7 @@
       </c>
       <c r="S50" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T50" s="31" t="str">
         <f t="shared" si="9"/>
@@ -9006,15 +8942,15 @@
         <v>Connection in which two branches are removed from the main route of the cable conveyor simultaneously.</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="61">
         <v>51</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C51" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>511</v>
@@ -9042,7 +8978,7 @@
       </c>
       <c r="L51" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M51" s="35" t="str">
         <f t="shared" si="6"/>
@@ -9067,7 +9003,7 @@
       </c>
       <c r="S51" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T51" s="31" t="str">
         <f t="shared" si="9"/>
@@ -9098,15 +9034,15 @@
         <v>Connection to normally more than two ports used to redistribute flow between ports.</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="61">
         <v>52</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C52" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>511</v>
@@ -9134,7 +9070,7 @@
       </c>
       <c r="L52" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M52" s="35" t="str">
         <f t="shared" si="6"/>
@@ -9159,7 +9095,7 @@
       </c>
       <c r="S52" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T52" s="31" t="str">
         <f t="shared" si="9"/>
@@ -9190,15 +9126,15 @@
         <v>Connection that changes the physical size of the cable carrier's main route.</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="61">
         <v>53</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C53" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>511</v>
@@ -9226,7 +9162,7 @@
       </c>
       <c r="L53" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M53" s="35" t="str">
         <f t="shared" si="6"/>
@@ -9251,7 +9187,7 @@
       </c>
       <c r="S53" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T53" s="31" t="str">
         <f t="shared" si="9"/>
@@ -9282,15 +9218,15 @@
         <v>Connection in which a branch is removed from the main route of the cable carrier.</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="61">
         <v>54</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>511</v>
@@ -9318,7 +9254,7 @@
       </c>
       <c r="L54" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M54" s="35" t="str">
         <f t="shared" si="6"/>
@@ -9343,7 +9279,7 @@
       </c>
       <c r="S54" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T54" s="31" t="str">
         <f t="shared" si="9"/>
@@ -9374,15 +9310,15 @@
         <v>Connection with normally two ports with different shapes or sizes.</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="61">
         <v>55</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C55" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>511</v>
@@ -9410,7 +9346,7 @@
       </c>
       <c r="L55" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M55" s="35" t="str">
         <f t="shared" si="6"/>
@@ -9435,7 +9371,7 @@
       </c>
       <c r="S55" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T55" s="31" t="str">
         <f t="shared" si="9"/>
@@ -9466,15 +9402,15 @@
         <v>Cable segments are a flow segments used to carry electrical power, data, or signals.</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="61">
         <v>56</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>511</v>
@@ -9502,7 +9438,7 @@
       </c>
       <c r="L56" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M56" s="35" t="str">
         <f t="shared" si="6"/>
@@ -9527,7 +9463,7 @@
       </c>
       <c r="S56" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T56" s="31" t="str">
         <f t="shared" si="9"/>
@@ -9558,15 +9494,15 @@
         <v>A single linear element within a cable or an exposed wire (such as for grounding).</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="61">
         <v>57</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C57" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>511</v>
@@ -9594,7 +9530,7 @@
       </c>
       <c r="L57" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M57" s="35" t="str">
         <f t="shared" si="6"/>
@@ -9619,7 +9555,7 @@
       </c>
       <c r="S57" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T57" s="31" t="str">
         <f t="shared" si="9"/>
@@ -9650,15 +9586,15 @@
         <v>Fiber segments is an individual optical fiber used in telecommunications systems to transmit data.</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="61">
         <v>58</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C58" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>511</v>
@@ -9686,7 +9622,7 @@
       </c>
       <c r="L58" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M58" s="35" t="str">
         <f t="shared" si="6"/>
@@ -9711,7 +9647,7 @@
       </c>
       <c r="S58" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T58" s="31" t="str">
         <f t="shared" si="9"/>
@@ -9742,15 +9678,15 @@
         <v>Optical cable segments is a cable segment that contains a variable number of fiber segments.</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="61">
         <v>59</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C59" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>511</v>
@@ -9778,7 +9714,7 @@
       </c>
       <c r="L59" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M59" s="35" t="str">
         <f t="shared" si="6"/>
@@ -9803,7 +9739,7 @@
       </c>
       <c r="S59" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T59" s="31" t="str">
         <f t="shared" si="9"/>
@@ -9834,15 +9770,15 @@
         <v>Pair of conductors contained in a copper cable.</v>
       </c>
     </row>
-    <row r="60" spans="1:27" s="68" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:27" s="68" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="61">
         <v>60</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C60" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>511</v>
@@ -9870,7 +9806,7 @@
       </c>
       <c r="L60" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M60" s="35" t="str">
         <f t="shared" si="6"/>
@@ -9895,7 +9831,7 @@
       </c>
       <c r="S60" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T60" s="31" t="str">
         <f t="shared" si="9"/>
@@ -9926,15 +9862,15 @@
         <v>A cable accessory is a part placed at a junction, transition, or termination in a system.</v>
       </c>
     </row>
-    <row r="61" spans="1:27" s="68" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:27" s="68" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="61">
         <v>61</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C61" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>511</v>
@@ -9962,7 +9898,7 @@
       </c>
       <c r="L61" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M61" s="35" t="str">
         <f t="shared" si="6"/>
@@ -9987,7 +9923,7 @@
       </c>
       <c r="S61" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T61" s="31" t="str">
         <f t="shared" si="9"/>
@@ -10018,15 +9954,15 @@
         <v>Accessory that joins two cable segments of the same connector type (although potentially different.</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="68" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:27" s="68" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="61">
         <v>62</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C62" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>511</v>
@@ -10054,7 +9990,7 @@
       </c>
       <c r="L62" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M62" s="35" t="str">
         <f t="shared" si="6"/>
@@ -10079,7 +10015,7 @@
       </c>
       <c r="S62" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T62" s="31" t="str">
         <f t="shared" si="9"/>
@@ -10110,15 +10046,15 @@
         <v>A connection that initiates a cable segment on a non-electrical element, such as a connected ground clamp.</v>
       </c>
     </row>
-    <row r="63" spans="1:27" s="68" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:27" s="68" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="61">
         <v>63</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C63" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>511</v>
@@ -10146,7 +10082,7 @@
       </c>
       <c r="L63" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M63" s="35" t="str">
         <f t="shared" si="6"/>
@@ -10171,7 +10107,7 @@
       </c>
       <c r="S63" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T63" s="31" t="str">
         <f t="shared" si="9"/>
@@ -10202,15 +10138,15 @@
         <v>A connection that terminates a cable segment in a non-electrical element, such as a connected ground clamp.</v>
       </c>
     </row>
-    <row r="64" spans="1:27" s="68" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:27" s="68" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="61">
         <v>64</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C64" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>511</v>
@@ -10238,7 +10174,7 @@
       </c>
       <c r="L64" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M64" s="35" t="str">
         <f t="shared" si="6"/>
@@ -10263,7 +10199,7 @@
       </c>
       <c r="S64" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T64" s="31" t="str">
         <f t="shared" si="9"/>
@@ -10294,15 +10230,15 @@
         <v>Fan out is a special cable connection that provides a safe transition from multi-fiber cable units.</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="61">
         <v>65</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C65" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>511</v>
@@ -10330,7 +10266,7 @@
       </c>
       <c r="L65" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M65" s="35" t="str">
         <f t="shared" si="6"/>
@@ -10355,7 +10291,7 @@
       </c>
       <c r="S65" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T65" s="31" t="str">
         <f t="shared" si="9"/>
@@ -10386,15 +10322,15 @@
         <v>Accessory that joins three or more segments of arbitrary connector types for signal splitting.</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="61">
         <v>66</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C66" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>511</v>
@@ -10422,7 +10358,7 @@
       </c>
       <c r="L66" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M66" s="35" t="str">
         <f t="shared" si="6"/>
@@ -10447,7 +10383,7 @@
       </c>
       <c r="S66" s="31" t="str">
         <f t="shared" si="19"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T66" s="31" t="str">
         <f t="shared" si="9"/>
@@ -10478,15 +10414,15 @@
         <v>Accessory that joins two cable segments of different types of connectors.</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="61">
         <v>67</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C67" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>511</v>
@@ -10514,7 +10450,7 @@
       </c>
       <c r="L67" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M67" s="35" t="str">
         <f t="shared" si="6"/>
@@ -10568,15 +10504,15 @@
         <v>250</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="61">
         <v>68</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C68" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>511</v>
@@ -10604,7 +10540,7 @@
       </c>
       <c r="L68" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M68" s="35" t="str">
         <f t="shared" si="6"/>
@@ -10658,15 +10594,15 @@
         <v>479</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="61">
         <v>69</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C69" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>511</v>
@@ -10694,7 +10630,7 @@
       </c>
       <c r="L69" s="35" t="str">
         <f t="shared" si="5"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M69" s="35" t="str">
         <f t="shared" si="6"/>
@@ -10748,15 +10684,15 @@
         <v>480</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="61">
         <v>70</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C70" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>511</v>
@@ -10784,7 +10720,7 @@
       </c>
       <c r="L70" s="35" t="str">
         <f t="shared" ref="L70:L133" si="29">CONCATENATE("", C70)</f>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M70" s="35" t="str">
         <f t="shared" ref="M70:M85" si="30">CONCATENATE("", D70)</f>
@@ -10838,15 +10774,15 @@
         <v>481</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="61">
         <v>71</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C71" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>511</v>
@@ -10874,7 +10810,7 @@
       </c>
       <c r="L71" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M71" s="35" t="str">
         <f t="shared" si="30"/>
@@ -10928,15 +10864,15 @@
         <v>482</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="61">
         <v>72</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C72" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>511</v>
@@ -10964,7 +10900,7 @@
       </c>
       <c r="L72" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M72" s="35" t="str">
         <f t="shared" si="30"/>
@@ -11018,15 +10954,15 @@
         <v>483</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="61">
         <v>73</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C73" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>511</v>
@@ -11054,7 +10990,7 @@
       </c>
       <c r="L73" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M73" s="35" t="str">
         <f t="shared" si="30"/>
@@ -11108,15 +11044,15 @@
         <v>484</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="61">
         <v>74</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C74" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>511</v>
@@ -11144,7 +11080,7 @@
       </c>
       <c r="L74" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M74" s="35" t="str">
         <f t="shared" si="30"/>
@@ -11198,15 +11134,15 @@
         <v>485</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="61">
         <v>75</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C75" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>511</v>
@@ -11234,7 +11170,7 @@
       </c>
       <c r="L75" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M75" s="35" t="str">
         <f t="shared" si="30"/>
@@ -11288,15 +11224,15 @@
         <v>486</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="61">
         <v>76</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C76" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>511</v>
@@ -11324,7 +11260,7 @@
       </c>
       <c r="L76" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M76" s="35" t="str">
         <f t="shared" si="30"/>
@@ -11378,15 +11314,15 @@
         <v>487</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="61">
         <v>77</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C77" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>511</v>
@@ -11414,7 +11350,7 @@
       </c>
       <c r="L77" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M77" s="35" t="str">
         <f t="shared" si="30"/>
@@ -11468,15 +11404,15 @@
         <v>487</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="61">
         <v>78</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C78" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>511</v>
@@ -11504,7 +11440,7 @@
       </c>
       <c r="L78" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M78" s="35" t="str">
         <f t="shared" si="30"/>
@@ -11558,15 +11494,15 @@
         <v>488</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="61">
         <v>79</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C79" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>511</v>
@@ -11594,7 +11530,7 @@
       </c>
       <c r="L79" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M79" s="35" t="str">
         <f t="shared" si="30"/>
@@ -11648,15 +11584,15 @@
         <v>489</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="61">
         <v>80</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C80" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>511</v>
@@ -11684,7 +11620,7 @@
       </c>
       <c r="L80" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M80" s="35" t="str">
         <f t="shared" si="30"/>
@@ -11738,15 +11674,15 @@
         <v>490</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="61">
         <v>81</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C81" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>511</v>
@@ -11774,7 +11710,7 @@
       </c>
       <c r="L81" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M81" s="35" t="str">
         <f t="shared" si="30"/>
@@ -11828,15 +11764,15 @@
         <v>491</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="61">
         <v>82</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C82" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>511</v>
@@ -11864,7 +11800,7 @@
       </c>
       <c r="L82" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M82" s="35" t="str">
         <f t="shared" si="30"/>
@@ -11918,15 +11854,15 @@
         <v>492</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="61">
         <v>83</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C83" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>511</v>
@@ -11954,7 +11890,7 @@
       </c>
       <c r="L83" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M83" s="35" t="str">
         <f t="shared" si="30"/>
@@ -12008,15 +11944,15 @@
         <v>493</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="61">
         <v>84</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C84" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>511</v>
@@ -12044,7 +11980,7 @@
       </c>
       <c r="L84" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M84" s="35" t="str">
         <f t="shared" si="30"/>
@@ -12098,15 +12034,15 @@
         <v>494</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="61">
         <v>85</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C85" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>511</v>
@@ -12134,7 +12070,7 @@
       </c>
       <c r="L85" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M85" s="35" t="str">
         <f t="shared" si="30"/>
@@ -12188,15 +12124,15 @@
         <v>543</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="61">
         <v>86</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C86" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>511</v>
@@ -12224,7 +12160,7 @@
       </c>
       <c r="L86" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M86" s="35" t="str">
         <f t="shared" ref="M86:M107" si="33">CONCATENATE("", D86)</f>
@@ -12278,15 +12214,15 @@
         <v>544</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="61">
         <v>87</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C87" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>511</v>
@@ -12314,7 +12250,7 @@
       </c>
       <c r="L87" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M87" s="35" t="str">
         <f t="shared" si="33"/>
@@ -12368,15 +12304,15 @@
         <v>545</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="61">
         <v>88</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C88" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>511</v>
@@ -12404,7 +12340,7 @@
       </c>
       <c r="L88" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M88" s="35" t="str">
         <f t="shared" si="33"/>
@@ -12458,15 +12394,15 @@
         <v>546</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="61">
         <v>89</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C89" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>511</v>
@@ -12494,7 +12430,7 @@
       </c>
       <c r="L89" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M89" s="35" t="str">
         <f t="shared" si="33"/>
@@ -12548,15 +12484,15 @@
         <v>547</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="61">
         <v>90</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C90" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>511</v>
@@ -12584,7 +12520,7 @@
       </c>
       <c r="L90" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M90" s="35" t="str">
         <f t="shared" si="33"/>
@@ -12638,15 +12574,15 @@
         <v>548</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="61">
         <v>91</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C91" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>511</v>
@@ -12674,7 +12610,7 @@
       </c>
       <c r="L91" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M91" s="35" t="str">
         <f t="shared" si="33"/>
@@ -12728,15 +12664,15 @@
         <v>549</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="61">
         <v>92</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C92" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>511</v>
@@ -12764,7 +12700,7 @@
       </c>
       <c r="L92" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M92" s="35" t="str">
         <f t="shared" si="33"/>
@@ -12818,15 +12754,15 @@
         <v>550</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="61">
         <v>93</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C93" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>511</v>
@@ -12854,7 +12790,7 @@
       </c>
       <c r="L93" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M93" s="35" t="str">
         <f t="shared" si="33"/>
@@ -12879,7 +12815,7 @@
       </c>
       <c r="S93" s="31" t="str">
         <f t="shared" ref="S93:S98" si="34">SUBSTITUTE(C93, "_", " ")</f>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T93" s="31" t="str">
         <f t="shared" si="32"/>
@@ -12910,15 +12846,15 @@
         <v>Electric motor is a motor that is a machine for converting electrical energy into mechanical energy.</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="61">
         <v>94</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C94" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>511</v>
@@ -12946,7 +12882,7 @@
       </c>
       <c r="L94" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M94" s="35" t="str">
         <f t="shared" si="33"/>
@@ -12971,7 +12907,7 @@
       </c>
       <c r="S94" s="31" t="str">
         <f t="shared" si="34"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T94" s="31" t="str">
         <f t="shared" si="32"/>
@@ -13002,15 +12938,15 @@
         <v>Motor that uses direct current (DC) power generated or rectified.</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="61">
         <v>95</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C95" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>511</v>
@@ -13038,7 +12974,7 @@
       </c>
       <c r="L95" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M95" s="35" t="str">
         <f t="shared" si="33"/>
@@ -13063,7 +12999,7 @@
       </c>
       <c r="S95" s="31" t="str">
         <f t="shared" si="34"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T95" s="31" t="str">
         <f t="shared" si="32"/>
@@ -13094,15 +13030,15 @@
         <v>Alternating current motor in which the primary winding on a member (usually the stator).</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="61">
         <v>96</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C96" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>511</v>
@@ -13130,7 +13066,7 @@
       </c>
       <c r="L96" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M96" s="35" t="str">
         <f t="shared" si="33"/>
@@ -13155,7 +13091,7 @@
       </c>
       <c r="S96" s="31" t="str">
         <f t="shared" si="34"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T96" s="31" t="str">
         <f t="shared" si="32"/>
@@ -13186,15 +13122,15 @@
         <v>Two-phase or three-phase induction motor in which the windings, one for each phase, are evenly divided.</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="61">
         <v>97</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C97" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>511</v>
@@ -13222,7 +13158,7 @@
       </c>
       <c r="L97" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M97" s="35" t="str">
         <f t="shared" si="33"/>
@@ -13247,7 +13183,7 @@
       </c>
       <c r="S97" s="31" t="str">
         <f t="shared" si="34"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T97" s="31" t="str">
         <f t="shared" si="32"/>
@@ -13278,15 +13214,15 @@
         <v>Synchronous motor with a special rotor design that directly aligns the rotor with the rotating rotor.</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="61">
         <v>98</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C98" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>511</v>
@@ -13314,7 +13250,7 @@
       </c>
       <c r="L98" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M98" s="35" t="str">
         <f t="shared" si="33"/>
@@ -13339,7 +13275,7 @@
       </c>
       <c r="S98" s="31" t="str">
         <f t="shared" si="34"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T98" s="31" t="str">
         <f t="shared" si="32"/>
@@ -13370,15 +13306,15 @@
         <v>Motor that operates at a constant speed until full load.</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="61">
         <v>99</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C99" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>511</v>
@@ -13406,7 +13342,7 @@
       </c>
       <c r="L99" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M99" s="35" t="str">
         <f t="shared" si="33"/>
@@ -13461,15 +13397,15 @@
         <v>It stores energy in chemical form so that it can be released as electrical energy.</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="61">
         <v>100</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C100" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>511</v>
@@ -13497,7 +13433,7 @@
       </c>
       <c r="L100" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M100" s="35" t="str">
         <f t="shared" si="33"/>
@@ -13552,15 +13488,15 @@
         <v>It stores electrical charge when an external power supply is present.</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="61">
         <v>101</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C101" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>511</v>
@@ -13588,7 +13524,7 @@
       </c>
       <c r="L101" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M101" s="35" t="str">
         <f t="shared" si="33"/>
@@ -13643,15 +13579,15 @@
         <v>It stores electrical energy when an external power supply.</v>
       </c>
     </row>
-    <row r="102" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="61">
         <v>102</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C102" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>511</v>
@@ -13679,7 +13615,7 @@
       </c>
       <c r="L102" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M102" s="35" t="str">
         <f t="shared" si="33"/>
@@ -13734,15 +13670,15 @@
         <v>Fix or adjust the electrical power parameter, such as voltage or power loss.</v>
       </c>
     </row>
-    <row r="103" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="61">
         <v>103</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C103" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>511</v>
@@ -13770,7 +13706,7 @@
       </c>
       <c r="L103" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M103" s="35" t="str">
         <f t="shared" si="33"/>
@@ -13825,15 +13761,15 @@
         <v>It constantly injects currents that precisely correspond to the designed harmonic components.</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="61">
         <v>104</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C104" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>511</v>
@@ -13861,7 +13797,7 @@
       </c>
       <c r="L104" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M104" s="35" t="str">
         <f t="shared" si="33"/>
@@ -13916,15 +13852,15 @@
         <v>Used in circuits or power systems due to its inductance, acting as a component of electrical.</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="61">
         <v>105</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C105" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>511</v>
@@ -13952,7 +13888,7 @@
       </c>
       <c r="L105" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M105" s="35" t="str">
         <f t="shared" si="33"/>
@@ -14007,15 +13943,15 @@
         <v>It stores electrical energy in a magnetic field using the electrical property of inductance.</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="61">
         <v>106</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C106" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>511</v>
@@ -14043,7 +13979,7 @@
       </c>
       <c r="L106" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M106" s="35" t="str">
         <f t="shared" si="33"/>
@@ -14098,15 +14034,15 @@
         <v>A battery charger is a device used to put power into a secondary or rechargeable cell.</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="61">
         <v>107</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C107" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>511</v>
@@ -14134,7 +14070,7 @@
       </c>
       <c r="L107" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M107" s="35" t="str">
         <f t="shared" si="33"/>
@@ -14189,15 +14125,15 @@
         <v>Provides an alternative power supply for a limited time in the event of a failure.</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="61">
         <v>108</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C108" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>511</v>
@@ -14225,7 +14161,7 @@
       </c>
       <c r="L108" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M108" s="35" t="str">
         <f t="shared" ref="M108:M123" si="37">CONCATENATE("", D108)</f>
@@ -14250,7 +14186,7 @@
       </c>
       <c r="S108" s="31" t="str">
         <f t="shared" ref="S108" si="38">SUBSTITUTE(C108, "_", " ")</f>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T108" s="31" t="str">
         <f t="shared" si="32"/>
@@ -14280,15 +14216,15 @@
         <v>402</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="61">
         <v>109</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C109" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>511</v>
@@ -14316,7 +14252,7 @@
       </c>
       <c r="L109" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M109" s="35" t="str">
         <f t="shared" si="37"/>
@@ -14341,7 +14277,7 @@
       </c>
       <c r="S109" s="31" t="str">
         <f t="shared" ref="S109:U136" si="39">SUBSTITUTE(C109, "_", " ")</f>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T109" s="31" t="str">
         <f t="shared" si="32"/>
@@ -14371,15 +14307,15 @@
         <v>435</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="61">
         <v>110</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C110" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>511</v>
@@ -14407,7 +14343,7 @@
       </c>
       <c r="L110" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M110" s="35" t="str">
         <f t="shared" si="37"/>
@@ -14432,7 +14368,7 @@
       </c>
       <c r="S110" s="31" t="str">
         <f t="shared" ref="S110:S113" si="40">SUBSTITUTE(C110, "_", " ")</f>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T110" s="31" t="str">
         <f t="shared" si="32"/>
@@ -14462,15 +14398,15 @@
         <v>399</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="61">
         <v>111</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C111" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>511</v>
@@ -14498,7 +14434,7 @@
       </c>
       <c r="L111" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M111" s="35" t="str">
         <f t="shared" si="37"/>
@@ -14523,7 +14459,7 @@
       </c>
       <c r="S111" s="31" t="str">
         <f t="shared" si="40"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T111" s="31" t="str">
         <f t="shared" si="32"/>
@@ -14553,15 +14489,15 @@
         <v>401</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="61">
         <v>112</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C112" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>511</v>
@@ -14570,7 +14506,7 @@
         <v>469</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G112" s="65" t="s">
         <v>9</v>
@@ -14589,7 +14525,7 @@
       </c>
       <c r="L112" s="35" t="str">
         <f t="shared" ref="L112" si="41">CONCATENATE("", C112)</f>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M112" s="35" t="str">
         <f t="shared" ref="M112" si="42">CONCATENATE("", D112)</f>
@@ -14614,7 +14550,7 @@
       </c>
       <c r="S112" s="31" t="str">
         <f t="shared" si="40"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T112" s="31" t="str">
         <f t="shared" ref="T112" si="45">SUBSTITUTE(D112, "_", " ")</f>
@@ -14644,15 +14580,15 @@
         <v>398</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="61">
         <v>113</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C113" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>511</v>
@@ -14680,7 +14616,7 @@
       </c>
       <c r="L113" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M113" s="35" t="str">
         <f t="shared" si="37"/>
@@ -14705,7 +14641,7 @@
       </c>
       <c r="S113" s="31" t="str">
         <f t="shared" si="40"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T113" s="31" t="str">
         <f t="shared" si="32"/>
@@ -14735,15 +14671,15 @@
         <v>403</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="61">
         <v>114</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C114" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>511</v>
@@ -14771,7 +14707,7 @@
       </c>
       <c r="L114" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M114" s="35" t="str">
         <f t="shared" si="37"/>
@@ -14796,7 +14732,7 @@
       </c>
       <c r="S114" s="31" t="str">
         <f t="shared" ref="S114" si="47">SUBSTITUTE(C114, "_", " ")</f>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T114" s="31" t="str">
         <f t="shared" si="32"/>
@@ -14826,15 +14762,15 @@
         <v>405</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="61">
         <v>115</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C115" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>511</v>
@@ -14862,7 +14798,7 @@
       </c>
       <c r="L115" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M115" s="35" t="str">
         <f t="shared" si="37"/>
@@ -14887,7 +14823,7 @@
       </c>
       <c r="S115" s="31" t="str">
         <f t="shared" ref="S115" si="48">SUBSTITUTE(C115, "_", " ")</f>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T115" s="31" t="str">
         <f t="shared" si="32"/>
@@ -14917,15 +14853,15 @@
         <v>400</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="61">
         <v>116</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C116" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>511</v>
@@ -14953,7 +14889,7 @@
       </c>
       <c r="L116" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M116" s="35" t="str">
         <f t="shared" si="37"/>
@@ -14978,7 +14914,7 @@
       </c>
       <c r="S116" s="31" t="str">
         <f t="shared" si="39"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T116" s="31" t="str">
         <f t="shared" si="32"/>
@@ -15008,15 +14944,15 @@
         <v>404</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="61">
         <v>117</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C117" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>511</v>
@@ -15044,7 +14980,7 @@
       </c>
       <c r="L117" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M117" s="35" t="str">
         <f t="shared" si="37"/>
@@ -15069,7 +15005,7 @@
       </c>
       <c r="S117" s="31" t="str">
         <f t="shared" si="39"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T117" s="31" t="str">
         <f t="shared" si="32"/>
@@ -15099,15 +15035,15 @@
         <v>406</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="61">
         <v>118</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C118" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>511</v>
@@ -15135,7 +15071,7 @@
       </c>
       <c r="L118" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M118" s="35" t="str">
         <f t="shared" si="37"/>
@@ -15160,7 +15096,7 @@
       </c>
       <c r="S118" s="31" t="str">
         <f t="shared" si="39"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T118" s="31" t="str">
         <f t="shared" si="32"/>
@@ -15190,15 +15126,15 @@
         <v>407</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="61">
         <v>119</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C119" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>511</v>
@@ -15226,7 +15162,7 @@
       </c>
       <c r="L119" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M119" s="35" t="str">
         <f t="shared" si="37"/>
@@ -15251,7 +15187,7 @@
       </c>
       <c r="S119" s="31" t="str">
         <f t="shared" si="39"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T119" s="31" t="str">
         <f t="shared" si="32"/>
@@ -15281,15 +15217,15 @@
         <v>408</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="61">
         <v>120</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C120" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>511</v>
@@ -15317,7 +15253,7 @@
       </c>
       <c r="L120" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M120" s="35" t="str">
         <f t="shared" si="37"/>
@@ -15342,7 +15278,7 @@
       </c>
       <c r="S120" s="31" t="str">
         <f t="shared" si="39"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T120" s="31" t="str">
         <f t="shared" si="32"/>
@@ -15372,15 +15308,15 @@
         <v>409</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="61">
         <v>121</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C121" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>511</v>
@@ -15408,7 +15344,7 @@
       </c>
       <c r="L121" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M121" s="35" t="str">
         <f t="shared" si="37"/>
@@ -15433,7 +15369,7 @@
       </c>
       <c r="S121" s="31" t="str">
         <f t="shared" si="39"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T121" s="31" t="str">
         <f t="shared" si="32"/>
@@ -15463,15 +15399,15 @@
         <v>410</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="61">
         <v>122</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C122" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>511</v>
@@ -15499,7 +15435,7 @@
       </c>
       <c r="L122" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M122" s="35" t="str">
         <f t="shared" si="37"/>
@@ -15524,7 +15460,7 @@
       </c>
       <c r="S122" s="31" t="str">
         <f t="shared" si="39"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T122" s="31" t="str">
         <f t="shared" si="32"/>
@@ -15554,15 +15490,15 @@
         <v>411</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="61">
         <v>123</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C123" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>511</v>
@@ -15590,7 +15526,7 @@
       </c>
       <c r="L123" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M123" s="35" t="str">
         <f t="shared" si="37"/>
@@ -15615,7 +15551,7 @@
       </c>
       <c r="S123" s="31" t="str">
         <f t="shared" si="39"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T123" s="31" t="str">
         <f t="shared" si="32"/>
@@ -15645,15 +15581,15 @@
         <v>412</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="61">
         <v>124</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C124" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>511</v>
@@ -15681,7 +15617,7 @@
       </c>
       <c r="L124" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M124" s="35" t="str">
         <f t="shared" ref="M124:M136" si="50">CONCATENATE("", D124)</f>
@@ -15706,7 +15642,7 @@
       </c>
       <c r="S124" s="31" t="str">
         <f t="shared" si="39"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T124" s="31" t="str">
         <f t="shared" si="32"/>
@@ -15736,15 +15672,15 @@
         <v>413</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="61">
         <v>125</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C125" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>511</v>
@@ -15772,7 +15708,7 @@
       </c>
       <c r="L125" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M125" s="35" t="str">
         <f t="shared" si="50"/>
@@ -15797,7 +15733,7 @@
       </c>
       <c r="S125" s="31" t="str">
         <f t="shared" si="39"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T125" s="31" t="str">
         <f t="shared" si="32"/>
@@ -15827,15 +15763,15 @@
         <v>414</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="61">
         <v>126</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C126" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>511</v>
@@ -15863,7 +15799,7 @@
       </c>
       <c r="L126" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M126" s="35" t="str">
         <f t="shared" si="50"/>
@@ -15888,7 +15824,7 @@
       </c>
       <c r="S126" s="31" t="str">
         <f t="shared" si="39"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T126" s="31" t="str">
         <f t="shared" si="32"/>
@@ -15918,15 +15854,15 @@
         <v>415</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="61">
         <v>127</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C127" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>511</v>
@@ -15954,7 +15890,7 @@
       </c>
       <c r="L127" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M127" s="35" t="str">
         <f t="shared" si="50"/>
@@ -15979,7 +15915,7 @@
       </c>
       <c r="S127" s="31" t="str">
         <f t="shared" ref="S127:S129" si="51">SUBSTITUTE(C127, "_", " ")</f>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T127" s="31" t="str">
         <f t="shared" si="32"/>
@@ -16009,15 +15945,15 @@
         <v>416</v>
       </c>
     </row>
-    <row r="128" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="61">
         <v>128</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C128" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>511</v>
@@ -16045,7 +15981,7 @@
       </c>
       <c r="L128" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M128" s="35" t="str">
         <f t="shared" si="50"/>
@@ -16070,7 +16006,7 @@
       </c>
       <c r="S128" s="31" t="str">
         <f t="shared" si="51"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T128" s="31" t="str">
         <f t="shared" si="32"/>
@@ -16100,15 +16036,15 @@
         <v>450</v>
       </c>
     </row>
-    <row r="129" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="61">
         <v>129</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C129" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>511</v>
@@ -16136,7 +16072,7 @@
       </c>
       <c r="L129" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M129" s="35" t="str">
         <f t="shared" si="50"/>
@@ -16161,7 +16097,7 @@
       </c>
       <c r="S129" s="31" t="str">
         <f t="shared" si="51"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T129" s="31" t="str">
         <f t="shared" si="32"/>
@@ -16191,15 +16127,15 @@
         <v>448</v>
       </c>
     </row>
-    <row r="130" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="61">
         <v>130</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C130" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>511</v>
@@ -16227,7 +16163,7 @@
       </c>
       <c r="L130" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M130" s="35" t="str">
         <f t="shared" si="50"/>
@@ -16252,7 +16188,7 @@
       </c>
       <c r="S130" s="31" t="str">
         <f t="shared" si="39"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T130" s="31" t="str">
         <f t="shared" si="32"/>
@@ -16282,21 +16218,21 @@
         <v>449</v>
       </c>
     </row>
-    <row r="131" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="61">
         <v>131</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C131" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>511</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F131" s="57" t="s">
         <v>347</v>
@@ -16318,7 +16254,7 @@
       </c>
       <c r="L131" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M131" s="35" t="str">
         <f t="shared" si="50"/>
@@ -16343,7 +16279,7 @@
       </c>
       <c r="S131" s="31" t="str">
         <f t="shared" si="39"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T131" s="31" t="str">
         <f t="shared" si="32"/>
@@ -16373,21 +16309,21 @@
         <v>417</v>
       </c>
     </row>
-    <row r="132" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="61">
         <v>132</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C132" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>511</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F132" s="57" t="s">
         <v>346</v>
@@ -16409,7 +16345,7 @@
       </c>
       <c r="L132" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M132" s="35" t="str">
         <f t="shared" si="50"/>
@@ -16434,7 +16370,7 @@
       </c>
       <c r="S132" s="31" t="str">
         <f t="shared" si="39"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T132" s="31" t="str">
         <f t="shared" si="32"/>
@@ -16464,15 +16400,15 @@
         <v>418</v>
       </c>
     </row>
-    <row r="133" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="61">
         <v>133</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C133" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>511</v>
@@ -16500,7 +16436,7 @@
       </c>
       <c r="L133" s="35" t="str">
         <f t="shared" si="29"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M133" s="35" t="str">
         <f t="shared" si="50"/>
@@ -16525,7 +16461,7 @@
       </c>
       <c r="S133" s="31" t="str">
         <f t="shared" si="39"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T133" s="31" t="str">
         <f t="shared" si="32"/>
@@ -16555,15 +16491,15 @@
         <v>426</v>
       </c>
     </row>
-    <row r="134" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="61">
         <v>134</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C134" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>511</v>
@@ -16591,7 +16527,7 @@
       </c>
       <c r="L134" s="35" t="str">
         <f t="shared" ref="L134:L142" si="53">CONCATENATE("", C134)</f>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M134" s="35" t="str">
         <f t="shared" si="50"/>
@@ -16616,7 +16552,7 @@
       </c>
       <c r="S134" s="31" t="str">
         <f t="shared" si="39"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T134" s="31" t="str">
         <f t="shared" si="32"/>
@@ -16646,15 +16582,15 @@
         <v>427</v>
       </c>
     </row>
-    <row r="135" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="61">
         <v>135</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C135" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>511</v>
@@ -16682,7 +16618,7 @@
       </c>
       <c r="L135" s="35" t="str">
         <f t="shared" si="53"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M135" s="35" t="str">
         <f t="shared" si="50"/>
@@ -16707,7 +16643,7 @@
       </c>
       <c r="S135" s="31" t="str">
         <f t="shared" si="39"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T135" s="31" t="str">
         <f t="shared" si="39"/>
@@ -16737,15 +16673,15 @@
         <v>428</v>
       </c>
     </row>
-    <row r="136" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="61">
         <v>136</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C136" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>511</v>
@@ -16773,7 +16709,7 @@
       </c>
       <c r="L136" s="35" t="str">
         <f t="shared" si="53"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M136" s="35" t="str">
         <f t="shared" si="50"/>
@@ -16798,7 +16734,7 @@
       </c>
       <c r="S136" s="31" t="str">
         <f t="shared" si="39"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T136" s="31" t="str">
         <f t="shared" si="39"/>
@@ -16828,15 +16764,15 @@
         <v>429</v>
       </c>
     </row>
-    <row r="137" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="61">
         <v>137</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C137" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>511</v>
@@ -16864,7 +16800,7 @@
       </c>
       <c r="L137" s="35" t="str">
         <f t="shared" si="53"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M137" s="35" t="str">
         <f t="shared" ref="M137:M142" si="55">CONCATENATE("", D137)</f>
@@ -16889,7 +16825,7 @@
       </c>
       <c r="S137" s="31" t="str">
         <f t="shared" ref="S137:U142" si="56">SUBSTITUTE(C137, "_", " ")</f>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T137" s="31" t="str">
         <f t="shared" si="56"/>
@@ -16919,15 +16855,15 @@
         <v>430</v>
       </c>
     </row>
-    <row r="138" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="61">
         <v>138</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C138" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>511</v>
@@ -16955,7 +16891,7 @@
       </c>
       <c r="L138" s="35" t="str">
         <f t="shared" si="53"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M138" s="35" t="str">
         <f t="shared" si="55"/>
@@ -16980,7 +16916,7 @@
       </c>
       <c r="S138" s="31" t="str">
         <f t="shared" si="56"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T138" s="31" t="str">
         <f t="shared" si="56"/>
@@ -17010,15 +16946,15 @@
         <v>431</v>
       </c>
     </row>
-    <row r="139" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="61">
         <v>139</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C139" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>511</v>
@@ -17046,7 +16982,7 @@
       </c>
       <c r="L139" s="35" t="str">
         <f t="shared" si="53"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M139" s="35" t="str">
         <f t="shared" si="55"/>
@@ -17071,7 +17007,7 @@
       </c>
       <c r="S139" s="31" t="str">
         <f t="shared" si="56"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T139" s="31" t="str">
         <f t="shared" si="56"/>
@@ -17101,15 +17037,15 @@
         <v>432</v>
       </c>
     </row>
-    <row r="140" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="61">
         <v>140</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C140" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>511</v>
@@ -17137,7 +17073,7 @@
       </c>
       <c r="L140" s="35" t="str">
         <f t="shared" si="53"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M140" s="35" t="str">
         <f t="shared" si="55"/>
@@ -17162,7 +17098,7 @@
       </c>
       <c r="S140" s="31" t="str">
         <f t="shared" si="56"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T140" s="31" t="str">
         <f t="shared" si="56"/>
@@ -17192,15 +17128,15 @@
         <v>433</v>
       </c>
     </row>
-    <row r="141" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="61">
         <v>141</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C141" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>511</v>
@@ -17228,7 +17164,7 @@
       </c>
       <c r="L141" s="35" t="str">
         <f t="shared" si="53"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M141" s="35" t="str">
         <f t="shared" si="55"/>
@@ -17253,7 +17189,7 @@
       </c>
       <c r="S141" s="31" t="str">
         <f t="shared" si="56"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T141" s="31" t="str">
         <f t="shared" si="56"/>
@@ -17283,15 +17219,15 @@
         <v>434</v>
       </c>
     </row>
-    <row r="142" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="61">
         <v>142</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C142" s="34" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>511</v>
@@ -17319,7 +17255,7 @@
       </c>
       <c r="L142" s="35" t="str">
         <f t="shared" si="53"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="M142" s="35" t="str">
         <f t="shared" si="55"/>
@@ -17344,7 +17280,7 @@
       </c>
       <c r="S142" s="31" t="str">
         <f t="shared" si="56"/>
-        <v>EletroTécnico</v>
+        <v>EletroTécnicos</v>
       </c>
       <c r="T142" s="31" t="str">
         <f t="shared" si="56"/>
@@ -17380,153 +17316,153 @@
     <sortCondition ref="F7:F220"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A2:B142">
+    <cfRule type="cellIs" dxfId="78" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:O1 R1:X1 Z1">
-    <cfRule type="cellIs" dxfId="84" priority="389" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="389" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="83" priority="1825"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="1825"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F6">
+    <cfRule type="duplicateValues" dxfId="75" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F11">
-    <cfRule type="duplicateValues" dxfId="78" priority="1838"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="1838"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="77" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25:F38">
-    <cfRule type="duplicateValues" dxfId="76" priority="2187"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="2187"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39:F44">
-    <cfRule type="duplicateValues" dxfId="75" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39:F46">
-    <cfRule type="duplicateValues" dxfId="71" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F47:F54">
-    <cfRule type="duplicateValues" dxfId="68" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F55">
-    <cfRule type="duplicateValues" dxfId="64" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F56">
-    <cfRule type="duplicateValues" dxfId="63" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F57">
-    <cfRule type="duplicateValues" dxfId="59" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F58">
-    <cfRule type="duplicateValues" dxfId="55" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59">
-    <cfRule type="duplicateValues" dxfId="51" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F60:F64 F47:F54">
-    <cfRule type="duplicateValues" dxfId="47" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F60:F66 F47:F55">
-    <cfRule type="duplicateValues" dxfId="46" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F65:F66">
-    <cfRule type="duplicateValues" dxfId="44" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F67:F85 F1 F7:F38 F99:F1048576">
-    <cfRule type="duplicateValues" dxfId="43" priority="2192"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="2192"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F93:F98">
-    <cfRule type="duplicateValues" dxfId="42" priority="239"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="240"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="241"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="242"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="243"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="244"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="245"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="246"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="241"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="245"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="246"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F99:F107">
-    <cfRule type="duplicateValues" dxfId="34" priority="1886"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="1886"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F109">
-    <cfRule type="duplicateValues" dxfId="33" priority="1948"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="1948"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F124:F141 F109">
-    <cfRule type="duplicateValues" dxfId="32" priority="2037"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="2037"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F124:F1048576 F109 F99:F107 F67:F85 F1 F7:F38">
-    <cfRule type="duplicateValues" dxfId="31" priority="2198"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="2198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F133:F141 F109">
-    <cfRule type="duplicateValues" dxfId="30" priority="361"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="361"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F133:F141">
-    <cfRule type="duplicateValues" dxfId="29" priority="358"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="358"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F142">
-    <cfRule type="duplicateValues" dxfId="28" priority="297"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="297"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F142:F1048576 F67 F12:F24">
-    <cfRule type="duplicateValues" dxfId="27" priority="2209"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="2206"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="2207"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="2208"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="2209"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="2206"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="2207"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="2208"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="X12:X38 X67:X142">
-    <cfRule type="containsText" dxfId="23" priority="216" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="16" priority="216" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",X12)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AA2:AA6">
+    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AA39:AA66">
-    <cfRule type="cellIs" dxfId="21" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="49" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA85:AA92">
-    <cfRule type="duplicateValues" dxfId="20" priority="278"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="279"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="280"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="282"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="283"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="281"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="278"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="279"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="280"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="282"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="283"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="281"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA93:AA98">
-    <cfRule type="cellIs" dxfId="14" priority="238" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B142">
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="238" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17538,15 +17474,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -17611,7 +17547,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -17676,7 +17612,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -17743,7 +17679,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17759,30 +17695,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S11"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.42578125" customWidth="1"/>
-    <col min="5" max="5" width="7.140625" customWidth="1"/>
-    <col min="6" max="6" width="5.28515625" customWidth="1"/>
-    <col min="7" max="7" width="32.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" customWidth="1"/>
-    <col min="9" max="9" width="9.42578125" customWidth="1"/>
-    <col min="10" max="10" width="4.42578125" customWidth="1"/>
-    <col min="11" max="11" width="8.5703125" customWidth="1"/>
-    <col min="12" max="12" width="3.5703125" customWidth="1"/>
-    <col min="13" max="13" width="4.5703125" customWidth="1"/>
-    <col min="14" max="14" width="6.42578125" customWidth="1"/>
-    <col min="15" max="15" width="6.28515625" customWidth="1"/>
-    <col min="16" max="16" width="4.7109375" customWidth="1"/>
-    <col min="17" max="17" width="1.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.7109375" customWidth="1"/>
-    <col min="19" max="19" width="1.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3828125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.3828125" customWidth="1"/>
+    <col min="5" max="5" width="7.15234375" customWidth="1"/>
+    <col min="6" max="6" width="5.3046875" customWidth="1"/>
+    <col min="7" max="7" width="32.53515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.3046875" customWidth="1"/>
+    <col min="9" max="9" width="9.3828125" customWidth="1"/>
+    <col min="10" max="10" width="4.3828125" customWidth="1"/>
+    <col min="11" max="11" width="8.53515625" customWidth="1"/>
+    <col min="12" max="12" width="3.53515625" customWidth="1"/>
+    <col min="13" max="13" width="4.53515625" customWidth="1"/>
+    <col min="14" max="14" width="6.3828125" customWidth="1"/>
+    <col min="15" max="15" width="6.3046875" customWidth="1"/>
+    <col min="16" max="16" width="4.69140625" customWidth="1"/>
+    <col min="17" max="17" width="1.84375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.69140625" customWidth="1"/>
+    <col min="19" max="19" width="1.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
@@ -17841,7 +17777,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="21">
         <v>1</v>
       </c>
@@ -17900,7 +17836,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="21">
         <v>2</v>
       </c>
@@ -17959,7 +17895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="21">
         <v>3</v>
       </c>
@@ -17982,7 +17918,7 @@
         <v>505</v>
       </c>
       <c r="H4" s="51" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="I4" s="25" t="s">
         <v>509</v>
@@ -18018,7 +17954,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="21">
         <v>4</v>
       </c>
@@ -18041,7 +17977,7 @@
         <v>505</v>
       </c>
       <c r="H5" s="51" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="I5" s="25" t="s">
         <v>509</v>
@@ -18077,7 +18013,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="21">
         <v>5</v>
       </c>
@@ -18100,7 +18036,7 @@
         <v>505</v>
       </c>
       <c r="H6" s="51" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="I6" s="25" t="s">
         <v>509</v>
@@ -18136,7 +18072,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="21">
         <v>6</v>
       </c>
@@ -18159,7 +18095,7 @@
         <v>505</v>
       </c>
       <c r="H7" s="51" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="I7" s="25" t="s">
         <v>509</v>
@@ -18195,7 +18131,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="21">
         <v>7</v>
       </c>
@@ -18218,7 +18154,7 @@
         <v>505</v>
       </c>
       <c r="H8" s="51" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="I8" s="25" t="s">
         <v>509</v>
@@ -18254,7 +18190,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="21">
         <v>8</v>
       </c>
@@ -18277,7 +18213,7 @@
         <v>505</v>
       </c>
       <c r="H9" s="51" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="I9" s="25" t="s">
         <v>509</v>
@@ -18313,7 +18249,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="21">
         <v>9</v>
       </c>
@@ -18336,7 +18272,7 @@
         <v>505</v>
       </c>
       <c r="H10" s="51" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="I10" s="25" t="s">
         <v>509</v>
@@ -18372,7 +18308,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="21">
         <v>10</v>
       </c>
@@ -18395,7 +18331,7 @@
         <v>505</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="I11" s="25" t="s">
         <v>509</v>
@@ -18441,15 +18377,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="27" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="27" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="32">
         <v>0</v>
       </c>
@@ -18472,7 +18408,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="33">
         <v>2</v>
       </c>
@@ -18501,22 +18437,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="11" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
